--- a/rag/eval/results_new30/detailed_evaluation_new30.xlsx
+++ b/rag/eval/results_new30/detailed_evaluation_new30.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="All" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         </is>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD107" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         </is>
       </c>
       <c r="AG107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         </is>
       </c>
       <c r="AI107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         </is>
       </c>
       <c r="AK107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         </is>
       </c>
       <c r="AM107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="AO107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
